--- a/tables/itss1.xlsx
+++ b/tables/itss1.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,49 +429,49 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Наличие согласия</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Балл Физика/ИКТ</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Балл Русский язык</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Балл Математика</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Балл за индивидуальные достижения</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Сумма баллов</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="n">
@@ -469,26 +481,26 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="F2" t="n">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>236</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B3" t="n">
@@ -498,55 +510,55 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
+        <v>75</v>
+      </c>
+      <c r="F3" t="n">
         <v>67</v>
       </c>
-      <c r="F3" t="n">
-        <v>76</v>
-      </c>
       <c r="G3" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>218</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
         <v>2</v>
       </c>
       <c r="C4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G4" t="n">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>242</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B5" t="n">
@@ -559,23 +571,23 @@
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="F5" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="G5" t="n">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B6" t="n">
@@ -588,23 +600,23 @@
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="F6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>198</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B7" t="n">
@@ -614,26 +626,26 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F7" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G7" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>247</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B8" t="n">
@@ -646,139 +658,139 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="F8" t="n">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>237</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B9" t="n">
         <v>9</v>
       </c>
       <c r="C9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="F9" t="n">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="G9" t="n">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>247</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B10" t="n">
         <v>10</v>
       </c>
       <c r="C10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="F10" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="G10" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>219</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B11" t="n">
         <v>26</v>
       </c>
       <c r="C11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="F11" t="n">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="G11" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>246</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B12" t="n">
         <v>27</v>
       </c>
       <c r="C12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="F12" t="n">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="G12" t="n">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>257</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B13" t="n">
@@ -788,113 +800,113 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F13" t="n">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="G13" t="n">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>266</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B14" t="n">
         <v>29</v>
       </c>
       <c r="C14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F14" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="G14" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H14" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>219</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B15" t="n">
         <v>30</v>
       </c>
       <c r="C15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F15" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="G15" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="H15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B16" t="n">
         <v>31</v>
       </c>
       <c r="C16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="F16" t="n">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="G16" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>201</v>
+        <v>225</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B17" t="n">
@@ -907,52 +919,52 @@
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="F17" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G17" t="n">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>201</v>
+        <v>237</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B18" t="n">
         <v>33</v>
       </c>
       <c r="C18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F18" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="G18" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="H18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>245</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B19" t="n">
@@ -965,23 +977,23 @@
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F19" t="n">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="G19" t="n">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I19" t="n">
-        <v>262</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B20" t="n">
@@ -997,49 +1009,49 @@
         <v>74</v>
       </c>
       <c r="F20" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G20" t="n">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>245</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B21" t="n">
         <v>64</v>
       </c>
       <c r="C21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="F21" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="G21" t="n">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I21" t="n">
-        <v>261</v>
+        <v>191</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B22" t="n">
@@ -1049,26 +1061,26 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="F22" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G22" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>257</v>
+        <v>224</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B23" t="n">
@@ -1081,23 +1093,23 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F23" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G23" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I23" t="n">
-        <v>222</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B24" t="n">
@@ -1107,171 +1119,171 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="F24" t="n">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="G24" t="n">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I24" t="n">
-        <v>206</v>
+        <v>244</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B25" t="n">
         <v>68</v>
       </c>
       <c r="C25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="F25" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="G25" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>230</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B26" t="n">
         <v>69</v>
       </c>
       <c r="C26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="F26" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G26" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
-        <v>241</v>
+        <v>212</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
+      <c r="A27" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B27" t="n">
         <v>70</v>
       </c>
       <c r="C27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F27" t="n">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="G27" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="H27" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>262</v>
+        <v>196</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
+      <c r="A28" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B28" t="n">
         <v>71</v>
       </c>
       <c r="C28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="F28" t="n">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="G28" t="n">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="H28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I28" t="n">
-        <v>210</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B29" t="n">
         <v>72</v>
       </c>
       <c r="C29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F29" t="n">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="G29" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>262</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
+      <c r="A30" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B30" t="n">
@@ -1284,52 +1296,52 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="F30" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="G30" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H30" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I30" t="n">
-        <v>217</v>
+        <v>246</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B31" t="n">
         <v>74</v>
       </c>
       <c r="C31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="F31" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G31" t="n">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="H31" t="n">
         <v>8</v>
       </c>
       <c r="I31" t="n">
-        <v>276</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
+      <c r="A32" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B32" t="n">
@@ -1342,23 +1354,23 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F32" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="G32" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H32" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
         <v>217</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
+      <c r="A33" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B33" t="n">
@@ -1368,142 +1380,142 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F33" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G33" t="n">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="H33" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I33" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
+      <c r="A34" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B34" t="n">
         <v>77</v>
       </c>
       <c r="C34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="F34" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="G34" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="H34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I34" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
+      <c r="A35" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B35" t="n">
         <v>78</v>
       </c>
       <c r="C35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="F35" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G35" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>222</v>
+        <v>233</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
+      <c r="A36" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B36" t="n">
         <v>79</v>
       </c>
       <c r="C36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="F36" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="G36" t="n">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I36" t="n">
-        <v>191</v>
+        <v>260</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
+      <c r="A37" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B37" t="n">
         <v>80</v>
       </c>
       <c r="C37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
         <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="F37" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="G37" t="n">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="H37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I37" t="n">
-        <v>216</v>
+        <v>236</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
+      <c r="A38" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B38" t="n">
@@ -1513,55 +1525,55 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="F38" t="n">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="G38" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>251</v>
+        <v>186</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
+      <c r="A39" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B39" t="n">
         <v>82</v>
       </c>
       <c r="C39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="F39" t="n">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="G39" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I39" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
+      <c r="A40" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B40" t="n">
@@ -1571,26 +1583,26 @@
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F40" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G40" t="n">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="H40" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>255</v>
+        <v>240</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
+      <c r="A41" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B41" t="n">
@@ -1603,168 +1615,168 @@
         <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="F41" t="n">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="G41" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="H41" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I41" t="n">
-        <v>195</v>
+        <v>217</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
+      <c r="A42" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B42" t="n">
         <v>85</v>
       </c>
       <c r="C42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="F42" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G42" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>237</v>
+        <v>207</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B43" t="n">
         <v>122</v>
       </c>
       <c r="C43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F43" t="n">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="G43" t="n">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>244</v>
+        <v>211</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
+      <c r="A44" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B44" t="n">
         <v>123</v>
       </c>
       <c r="C44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="F44" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G44" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I44" t="n">
-        <v>214</v>
+        <v>239</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
+      <c r="A45" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B45" t="n">
         <v>124</v>
       </c>
       <c r="C45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F45" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G45" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>237</v>
+        <v>251</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
+      <c r="A46" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B46" t="n">
         <v>125</v>
       </c>
       <c r="C46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="F46" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="G46" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>236</v>
+        <v>251</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
+      <c r="A47" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B47" t="n">
@@ -1777,23 +1789,23 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
+        <v>62</v>
+      </c>
+      <c r="F47" t="n">
+        <v>94</v>
+      </c>
+      <c r="G47" t="n">
         <v>84</v>
       </c>
-      <c r="F47" t="n">
-        <v>81</v>
-      </c>
-      <c r="G47" t="n">
-        <v>83</v>
-      </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
+      <c r="A48" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B48" t="n">
@@ -1806,23 +1818,23 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="F48" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="G48" t="n">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="H48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I48" t="n">
-        <v>263</v>
+        <v>199</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
+      <c r="A49" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B49" t="n">
@@ -1835,23 +1847,23 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="F49" t="n">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="G49" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="H49" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>231</v>
+        <v>199</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
+      <c r="A50" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B50" t="n">
@@ -1864,48 +1876,48 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F50" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="G50" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I50" t="n">
-        <v>206</v>
+        <v>228</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
+      <c r="A51" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B51" t="n">
         <v>130</v>
       </c>
       <c r="C51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F51" t="n">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="G51" t="n">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I51" t="n">
-        <v>289</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
